--- a/artfynd/A 42687-2022 artfynd.xlsx
+++ b/artfynd/A 42687-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42687-2022 artfynd.xlsx
+++ b/artfynd/A 42687-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64611454</v>
+        <v>64611487</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>803641.7681090399</v>
+        <v>803730</v>
       </c>
       <c r="R2" t="n">
-        <v>7147715.302438511</v>
+        <v>7147761</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,19 +749,9 @@
           <t>2013-11-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-11-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +779,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64611487</v>
+        <v>73094141</v>
       </c>
       <c r="B3" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,43 +790,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Aftonsmyrberget 3, Vb</t>
+          <t>Aftonsmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>803730.2874905637</v>
+        <v>803705</v>
       </c>
       <c r="R3" t="n">
-        <v>7147761.190271243</v>
+        <v>7147766</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-11-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-11-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,72 +858,72 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73094141</v>
+        <v>64611662</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aftonsmyrberget, Vb</t>
+          <t>Aftonsmyrberget 3, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>803704.8933597908</v>
+        <v>803597</v>
       </c>
       <c r="R4" t="n">
-        <v>7147766.087155087</v>
+        <v>7147614</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,22 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,21 +961,119 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>73094184</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Aftonsmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>803607</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7147612</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-09-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-09-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Emil Larsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Emil Larsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42687-2022 artfynd.xlsx
+++ b/artfynd/A 42687-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64611487</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73094141</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64611662</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,8 +1094,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73094184</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>